--- a/i_test/05_05_test_adding_PROMPT_T_and_LB/i_input_xlsx/D3_pregnancy_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT_T_and_LB/i_input_xlsx/D3_pregnancy_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT_T_and_LB\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B56A01E-C565-43F6-870D-621278E07F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1E259B-9082-48F6-899A-22485E561135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
